--- a/output/pdf_financials_xlsx/NWX.xlsx
+++ b/output/pdf_financials_xlsx/NWX.xlsx
@@ -4263,28 +4263,28 @@
         <v>1.173038</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.173038</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.173038</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.173038</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.4201</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.810559</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.028553</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.213537</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.213537</v>
       </c>
     </row>
     <row r="93">
@@ -7386,7 +7386,11 @@
           <t>Reserves (Note 9(c))</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -9642,7 +9646,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NWX.xlsx
+++ b/output/pdf_financials_xlsx/NWX.xlsx
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.1979</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.048798</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.08177</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.08851000000000001</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1674,16 +1674,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.517716</v>
+        <v>-0.715616</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.49223</v>
+        <v>-0.541028</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.386519</v>
+        <v>-0.468289</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.434381</v>
+        <v>-0.522891</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1772,16 +1772,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.517716</v>
+        <v>-0.715616</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.49223</v>
+        <v>-0.541028</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.386519</v>
+        <v>-0.468289</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.434381</v>
+        <v>-0.522891</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1991,28 +1991,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>7.437997</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>6.962715</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>5.49087</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.556163</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.452666</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.909372</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.243698</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0</v>
@@ -2065,28 +2065,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>7.437997</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>6.962715</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.025216</v>
+        <v>6.516086</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>3.445275</v>
+        <v>6.001438</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.311101</v>
+        <v>6.763767</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>16.001512</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>11.910544</v>
+        <v>12.819916</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.770549</v>
+        <v>3.014247</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>2.424537</v>
@@ -2509,28 +2509,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>7.437997</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.963723</v>
+        <v>0.001008</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.492041</v>
+        <v>0.001171</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.55869</v>
+        <v>0.002527</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.454624</v>
+        <v>0.001958</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>1.754167</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.987478</v>
+        <v>3.078106</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.541429</v>
+        <v>2.297731</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>2.869621</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
